--- a/my-blog/src/excel/游戏板块轮播图.xlsx
+++ b/my-blog/src/excel/游戏板块轮播图.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>是否导表</t>
   </si>
@@ -155,10 +155,22 @@
     <t>count</t>
   </si>
   <si>
-    <t>游戏标题1</t>
-  </si>
-  <si>
-    <t>标签1,标签2</t>
+    <t>Coser女友的养成方法</t>
+  </si>
+  <si>
+    <t>1_1</t>
+  </si>
+  <si>
+    <t>1_2</t>
+  </si>
+  <si>
+    <t>1_3</t>
+  </si>
+  <si>
+    <t>1_4</t>
+  </si>
+  <si>
+    <t>galgame,恋爱模拟</t>
   </si>
   <si>
     <t>这里是游戏简介1</t>
@@ -1158,7 +1170,9 @@
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="9.125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="15.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="9" width="16" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" customWidth="1"/>
@@ -1329,29 +1343,29 @@
       <c r="G4" s="1">
         <v>1</v>
       </c>
-      <c r="H4" s="1">
-        <v>2</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>2</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N4" s="1">
-        <v>48</v>
+        <v>19.8</v>
       </c>
       <c r="O4" s="1">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -1371,28 +1385,28 @@
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G5" s="1">
         <v>2</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1">
         <v>2</v>
       </c>
       <c r="J5" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5" s="1">
         <v>2</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N5" s="1">
         <v>72</v>
@@ -1418,28 +1432,28 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="1">
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="N6" s="1">
         <v>248</v>

--- a/my-blog/src/excel/游戏板块轮播图.xlsx
+++ b/my-blog/src/excel/游戏板块轮播图.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>是否导表</t>
   </si>
@@ -173,16 +173,28 @@
     <t>galgame,恋爱模拟</t>
   </si>
   <si>
-    <t>这里是游戏简介1</t>
-  </si>
-  <si>
-    <t>游戏标题2</t>
-  </si>
-  <si>
-    <t>标签1,标签3</t>
-  </si>
-  <si>
-    <t>这里是游戏简介2</t>
+    <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于成长、抉择与爱恋的故事，就此展开。</t>
+  </si>
+  <si>
+    <t>病狱</t>
+  </si>
+  <si>
+    <t>2_1</t>
+  </si>
+  <si>
+    <t>2_2</t>
+  </si>
+  <si>
+    <t>2_3</t>
+  </si>
+  <si>
+    <t>2_4</t>
+  </si>
+  <si>
+    <t>策略,角色扮演,卡牌游戏,回合战略,2D,像素,8-bit</t>
+  </si>
+  <si>
+    <t>然后，你醒了。冰冷的灯光透过散乱的发丝，在脸颊勾勒出时间的刻痕；脑海中的气泡破碎，只余下飞速消退的碎散浮沫。一切的意义都在溃散。你仍未知晓此地的一切，甚至包括自己在内；只是，仅剩的念头始终在脑海中萦绕，牵扯你迷惘的肉体和灵魂：“今天的治疗快要开始了”</t>
   </si>
   <si>
     <t>游戏标题3</t>
@@ -844,7 +856,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -853,6 +865,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1177,7 +1192,7 @@
     <col min="10" max="10" width="15.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="15" style="1" customWidth="1"/>
     <col min="12" max="12" width="26.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34.875" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.25" style="1" customWidth="1"/>
     <col min="15" max="15" width="15.5" style="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
@@ -1358,7 +1373,7 @@
       <c r="L4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="N4" s="1">
@@ -1382,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>37</v>
@@ -1390,29 +1405,26 @@
       <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>3</v>
-      </c>
-      <c r="K5" s="1">
-        <v>2</v>
+      <c r="H5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="N5" s="1">
-        <v>72</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1429,31 +1441,31 @@
         <v>3</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G6" s="1">
         <v>3</v>
       </c>
       <c r="H6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="1">
         <v>3</v>
       </c>
       <c r="J6" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
         <v>3</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N6" s="1">
         <v>248</v>

--- a/my-blog/src/excel/游戏板块轮播图.xlsx
+++ b/my-blog/src/excel/游戏板块轮播图.xlsx
@@ -173,7 +173,7 @@
     <t>galgame,恋爱模拟</t>
   </si>
   <si>
-    <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于成长、抉择与爱恋的故事，就此展开。</t>
+    <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于青春、成长与爱恋的故事，就此展开。</t>
   </si>
   <si>
     <t>病狱</t>
@@ -1377,7 +1377,7 @@
         <v>36</v>
       </c>
       <c r="N4" s="1">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="O4" s="1">
         <v>0.9</v>

--- a/my-blog/src/excel/游戏板块轮播图.xlsx
+++ b/my-blog/src/excel/游戏板块轮播图.xlsx
@@ -28,42 +28,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>27966</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>在dist/game_banner里</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="14"/>
-            <rFont val="微软雅黑"/>
-            <charset val="134"/>
-          </rPr>
-          <t>用，隔开</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>是否导表</t>
   </si>
@@ -80,36 +46,6 @@
     <t>游戏ID</t>
   </si>
   <si>
-    <t>游戏名</t>
-  </si>
-  <si>
-    <t>大图</t>
-  </si>
-  <si>
-    <t>小图1</t>
-  </si>
-  <si>
-    <t>小图2</t>
-  </si>
-  <si>
-    <t>小图3</t>
-  </si>
-  <si>
-    <t>小图4</t>
-  </si>
-  <si>
-    <t>标签组</t>
-  </si>
-  <si>
-    <t>简介</t>
-  </si>
-  <si>
-    <t>原价</t>
-  </si>
-  <si>
-    <t>折扣</t>
-  </si>
-  <si>
     <t>isload</t>
   </si>
   <si>
@@ -124,87 +60,6 @@
   <si>
     <t>game_id</t>
   </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>img_big</t>
-  </si>
-  <si>
-    <t>img_1</t>
-  </si>
-  <si>
-    <t>img_2</t>
-  </si>
-  <si>
-    <t>img_3</t>
-  </si>
-  <si>
-    <t>img_4</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>Coser女友的养成方法</t>
-  </si>
-  <si>
-    <t>1_1</t>
-  </si>
-  <si>
-    <t>1_2</t>
-  </si>
-  <si>
-    <t>1_3</t>
-  </si>
-  <si>
-    <t>1_4</t>
-  </si>
-  <si>
-    <t>galgame,恋爱模拟</t>
-  </si>
-  <si>
-    <t>一款以"和coser女友谈恋爱"为主题的恋爱轻喜剧galgame。在大学毕业前夕，你约了一场cos委托，阴差阳错的收获一个coser女友。在人生的叉路口，你们将走向何方？一段关于青春、成长与爱恋的故事，就此展开。</t>
-  </si>
-  <si>
-    <t>病狱</t>
-  </si>
-  <si>
-    <t>2_1</t>
-  </si>
-  <si>
-    <t>2_2</t>
-  </si>
-  <si>
-    <t>2_3</t>
-  </si>
-  <si>
-    <t>2_4</t>
-  </si>
-  <si>
-    <t>策略,角色扮演,卡牌游戏,回合战略,2D,像素,8-bit</t>
-  </si>
-  <si>
-    <t>然后，你醒了。冰冷的灯光透过散乱的发丝，在脸颊勾勒出时间的刻痕；脑海中的气泡破碎，只余下飞速消退的碎散浮沫。一切的意义都在溃散。你仍未知晓此地的一切，甚至包括自己在内；只是，仅剩的念头始终在脑海中萦绕，牵扯你迷惘的肉体和灵魂：“今天的治疗快要开始了”</t>
-  </si>
-  <si>
-    <t>游戏标题3</t>
-  </si>
-  <si>
-    <t>标签1,标签4,标签5</t>
-  </si>
-  <si>
-    <t>这里是游戏简介3</t>
-  </si>
 </sst>
 </file>
 
@@ -216,7 +71,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,16 +228,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -856,7 +701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -865,9 +710,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1180,25 +1022,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="5"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="9.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="9" width="16" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15" style="1" customWidth="1"/>
-    <col min="12" max="12" width="26.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="34.875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1214,85 +1047,25 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:5">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -1305,38 +1078,8 @@
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="1">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1">
-        <v>2</v>
-      </c>
-      <c r="J3" s="1">
-        <v>2</v>
-      </c>
-      <c r="K3" s="1">
-        <v>2</v>
-      </c>
-      <c r="L3" s="1">
-        <v>2</v>
-      </c>
-      <c r="M3" s="1">
-        <v>2</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1</v>
-      </c>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1352,38 +1095,8 @@
       <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="1">
-        <v>22</v>
-      </c>
-      <c r="O4" s="1">
-        <v>0.9</v>
-      </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1399,35 +1112,8 @@
       <c r="E5" s="1">
         <v>2</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1442,43 +1128,12 @@
       </c>
       <c r="E6" s="1">
         <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1">
-        <v>3</v>
-      </c>
-      <c r="J6" s="1">
-        <v>3</v>
-      </c>
-      <c r="K6" s="1">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N6" s="1">
-        <v>248</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
